--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -247,6 +247,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -906,12 +909,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>供給量と将来推計 第2段階の見込量を対照する。</t>
+          <t>供給量とサービス見込量の算定 第1次概算を対照する（計画素案 第6章と同じ値）。</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>施設・居住系はいずれも定員内に収まる。認定者の24.5％（486人）がサービスを利用していない。</t>
+          <t>施設・居住系は合計では定員内に収まるが、地域密着型介護老人福祉施設は令和11年度に定員62人の99.9％となる。認定者の24.5％（486人）がサービスを利用していない。在籍と受給は数える対象が異なり、介護老人保健施設だけが在籍206人＞受給134.1人／月である。</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -936,7 +939,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>母集団・時点・回収状況の3点に留保がある。点検事項35件のうち重大6件は取扱いの決定を要する。</t>
+          <t>母集団・時点・回収状況の3点に留保がある。点検事項35件のうち重大6件は取扱いの決定を要する。調査①が在宅の認定者全体を代表しないことはχ²＝43.5（自由度6。1％点16.81）として測定済みである。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -956,12 +959,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>所見と計画素案の反映先を対応させる。</t>
+          <t>所見と計画素案の反映先を対応させる。反映済みかどうかは計画素案の実物を読んで判定する。</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>所見20件。うち着手可11件、重大6件の決定待ち9件。</t>
+          <t>所見20件。反映済みのものは計画素案から機械的に判定する。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1011,7 +1014,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>解消6件・未解消4件・一部解消1件・公表待ち1件・決定待ち1件。訪問介護13事業所181人の全数把握により、訪問系の代表性の留保が解消した。</t>
+          <t>解消6件・測定済み3件・未解消3件・一部解消1件・公表待ち1件・決定待ち1件。訪問介護13事業所181人の全数把握により、訪問系の代表性の留保が解消した。令和8年9月11日に年報の要介護度別の明細を収めたことにより、調査①の偏りと、在籍と受給の違いを測定できるようになった。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1880,7 +1883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1901,7 +1904,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>供給量（06シート）と将来推計 第2段階の見込量を対照する。見込量は、利用率と受給者1人当たりの利用日数・回数を令和7年度の値で固定した基本ケースによる。</t>
+          <t>供給量（06シート）とサービス見込量の算定 第1次概算（令和8年9月16日。計画素案 第6章と同じ値）を対照する。見込量は、要介護度別の利用率と1人1月あたり給付費を令和7年度の値で固定した算定による。実績は年報（令和7年度）の月平均であり、保険者（広域連合）を単位として当広域連合の被保険者を数えたものである。</t>
         </is>
       </c>
     </row>
@@ -1914,13 +1917,13 @@
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t>令和7年度
-実績</t>
+実績（人／月）</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>令和11年度
-見込み</t>
+見込み（人／月）</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1940,62 +1943,62 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>施設サービス</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>336</v>
+        <v>337.1</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>339</v>
+        <v>352.3</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>462</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>73.4％</t>
+          <t>76.3％</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>定員に余裕がある。ただし特養の待機者は別に存在する</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
+          <t>合計では定員に収まるが、種別別では逼迫するものがある（地域密着型介護老人福祉施設は令和11年度に定員62人の99.9％）。特養の待機者は別に存在する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>居住系サービス</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>144</v>
+        <v>143.1</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>145</v>
+        <v>149.4</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>255</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>56.9％</t>
+          <t>58.6％</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>定員に余裕がある。区域内の施設には住所地特例により他保険者の被保険者も入居しており、差がそのまま空きを示すものではない</t>
+          <t>合計では定員に収まる。区域内の定員は当広域連合の被保険者にとっての上限ではない。年報は施設の所在地を問わず当広域連合の被保険者を数えるため、区域外の施設の利用が含まれる</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>【認定者の利用状況（令和7年度）】</t>
+          <t>【施設の側から数えた在籍者と、保険者の側から数えた受給者】</t>
         </is>
       </c>
     </row>
@@ -2007,15 +2010,22 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>推計人数</t>
+          <t>調査②
+在籍（人）</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>認定者に対する割合</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>年報 受給
+（人／月）</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>差
+（在籍−受給）</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2026,245 +2036,369 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>在宅サービス</t>
+          <t>グループホーム</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1016</v>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>51.2％</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="9" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>訪問・通所・短期入所等</t>
+          <t>受給＞在籍。当広域連合の被保険者が区域外の施設を利用している。区域内の定員では説明できない</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>居住系サービス</t>
+          <t>特定施設</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>145</v>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>7.3％</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="9" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>グループホーム・特定施設</t>
+          <t>受給＞在籍。当広域連合の被保険者が区域外の施設を利用している。区域内の定員では説明できない</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>施設サービス</t>
+          <t>特養・地域密着型特養</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>337</v>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>17.0％</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="9" t="n"/>
+        <v>146</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>特養・老健・地域密着型特養</t>
+          <t>受給＞在籍。当広域連合の被保険者が区域外の施設を利用している。区域内の定員では説明できない</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>いずれも利用していない</t>
+          <t>介護老人保健施設</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>486</v>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>24.5％</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="9" t="n"/>
+        <v>206</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>134.1</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>認定者1,984人の4分の1。健康とくらしの調査の「介護・介助が必要だが受けていない7.0％」とは別の集団であり、合算しない。内訳（資料依頼No.8）の受領後に要因を分解する</t>
+          <t>在籍＞受給。区域内の施設に他の保険者の被保険者が入居している（住所地特例を含む）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>【調査結果と供給構造の接続】</t>
+          <t>【認定者の利用状況（令和7年度）】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>調査で示されたこと</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr"/>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>推計人数</t>
+        </is>
+      </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>供給構造の側から見えること</t>
+          <t>認定者に対する割合</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>計画での扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>利用者票で必要とされた生活支援の最多は外出同行（51件・51.5％）である</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>訪問系13事業所のうち美瑛町を実施地域とするのは4事業所である。健康とくらしの調査では自力移動の手段がない層が20％台にある。</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="n"/>
+          <t>在宅サービス</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>1016</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>51.2％</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>移動の確保を第5章基本目標2の重点に位置づける。介護保険の給付では担えない部分は生活支援体制整備事業による</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="52" customHeight="1">
+          <t>訪問・通所・短期入所等</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>利用者票で夜間対応型・定期巡回・看多機が計26件挙げられた</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>この3サービスは区域内に事業所がなく、受給率も0.0％である。</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="n"/>
+          <t>居住系サービス</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>7.3％</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>第6章第4節（24時間対応サービスの確保方策）の根拠とする。整備するか、既存の訪問介護・訪問看護の連携で代替するかを決める</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
+          <t>グループホーム・特定施設</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>居所変更実態調査で新規入所の57.0％が病院・診療所からである</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>老健3施設240人が区域内の中間施設として機能している。在宅への復帰か施設入所かの分岐点が医療機関にある。</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="n"/>
+          <t>施設サービス</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>337</v>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>17.0％</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>第6章第5節（医療と介護の連携）の根拠とする</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52" customHeight="1">
+          <t>特養・老健・地域密着型特養</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>介護人材実態調査で介護職員の33.3％が見える化で把握できないサービスに従事している</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>グループホーム7・特定施設3・住宅型有料9・サ高住2・軽費1の22施設が該当する。うち調査に回答したのは一部にとどまる。</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="n"/>
+          <t>いずれも利用していない</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="n">
+        <v>486</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>24.5％</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
+          <t>認定者1,984人の4分の1。健康とくらしの調査の「介護・介助が必要だが受けていない7.0％」とは別の集団であり、合算しない。内訳（資料依頼No.8）の受領後に要因を分解する</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>【調査結果と供給構造の接続】</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>調査で示されたこと</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>供給構造の側から見えること</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>計画での扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>利用者票で必要とされた生活支援の最多は外出同行（51件・51.5％）である</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>訪問系13事業所のうち美瑛町を実施地域とするのは4事業所である。健康とくらしの調査では自力移動の手段がない層が20％台にある。</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>移動の確保を第5章基本目標2の重点に位置づける。介護保険の給付では担えない部分は生活支援体制整備事業による</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>利用者票で夜間対応型・定期巡回・看多機が計26件挙げられた</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>この3サービスは区域内に事業所がなく、受給率も0.0％である。</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>第6章第4節（24時間対応サービスの確保方策）の根拠とする。整備するか、既存の訪問介護・訪問看護の連携で代替するかを決める</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>居所変更実態調査で新規入所の57.0％が病院・診療所からである</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>老健3施設240人が区域内の中間施設として機能している。在宅への復帰か施設入所かの分岐点が医療機関にある。</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>第6章第5節（医療と介護の連携）の根拠とする</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>介護人材実態調査で介護職員の33.3％が見える化で把握できないサービスに従事している</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム7・特定施設3・住宅型有料9・サ高住2・軽費1の22施設が該当する。うち調査に回答したのは一部にとどまる。</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>第3章第5節では、把握範囲を明記したうえで記述する。本調査を継続する意義を第10期に位置づける</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>利用者票で小規模多機能が最多（44件）に挙げられた</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>区域内の小規模多機能5事業所はすべて1法人が美瑛町で運営し、東川町・東神楽町を実施地域とするのは1事業所のみである。</t>
         </is>
       </c>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>第6章第2節の見込量は町別の実施地域を踏まえて設定する。件数をそのまま需要の強さと読まない</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="91" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>注1）見込量は別冊「将来推計 第2段階　サービス見込量」（8シート）による。利用率と1人当たりの利用日数・回数の置き方はヒアリングシート項目6でご意向を確認する事項であり、確定していない。注2）本シートは、4調査を横断したクロス集計に代えて調査相互を接続するものである（13シート）。個票を突き合わせたものではなく、集計値と供給構造による対照である。注3）人数は、認定者数1,984人（令和8年3月末）に令和7年度の合計利用率（見える化D45系列）を乗じて算定した推計人数であり、月平均の受給者実績（在宅1,013人・居住系144人・施設336人）とは算定の方法が異なるため一致しない。4区分の合計は1,984人となる。注4）「いずれも利用していない486人」と健康とくらしの調査の「介護・介助が必要だが受けていない7.0％」は母集団が異なる（前者は認定者、後者は一般高齢者）。合算も比率の比較もしない。</t>
+    <row r="30" ht="130" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>注1）見込量は別冊「サービス見込量の算定 第1次概算」（18シート）による。計画素案 第6章に反映済みの値と同じである（令和8年9月16日。従前は将来推計 第2段階の値を掲げていた）。前提は確定しておらず、第2次概算（令和8年10月30日）により改まる。注2）本シートは、4調査を横断したクロス集計に代えて調査相互を接続するものである（13シート）。個票を突き合わせたものではなく、集計値と供給構造による対照である。注3）人数は、認定者数1,984人（令和8年3月末）に令和7年度の合計利用率（見える化D45系列）を乗じて算定した推計人数であり、月平均の受給者実績（在宅1,013人・居住系143.1人・施設337.1人）とは算定の方法が異なるため一致しない。4区分の合計は1,984人となる。注4）「いずれも利用していない486人」と健康とくらしの調査の「介護・介助が必要だが受けていない7.0％」は母集団が異なる（前者は認定者、後者は一般高齢者）。合算も比率の比較もしない。注5）在籍と受給は数える対象が異なる。年報（受給）は施設の所在地を問わず当広域連合の被保険者を数え、調査②（在籍）は保険者を問わず区域内の施設の在籍者を数える。介護老人保健施設だけが在籍206人＞受給134.1人／月（＋71.9人）であり、他の3区分は受給＞在籍である。したがって区域内の定員は必要利用定員総数の上限ではなく、到達率が100％を超えることは誤りではない（確認事項No.88・No.141）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="23">
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D19:E19"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="E12"/>
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="E10"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="E13"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="E11"/>
+    <mergeCell ref="C25:E25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2276,7 +2410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2363,12 +2497,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>「在宅生活の維持が困難72.7％」を区域内の在宅利用者全体の割合と読めない。</t>
+          <t>「在宅生活の維持が困難72.7％」を区域内の在宅利用者全体の割合と読めない。令和8年9月11日の突合により、偏りの大きさと向きを測定した。要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5、自由度6。1％点16.81）。要介護3は期待6.7人に対し19人（2.8倍）、要支援1は期待18.9人に対し3人（0.16倍）である。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>「調査対象となった99人のうち」と明記する。率ではなく実数で記述する。</t>
+          <t>「調査対象となった99人のうち」と明記する。率ではなく実数で記述する。「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない（確認事項No.140。突合クロス集計 02シート）。</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -2677,8 +2811,58 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>②の在籍者と年報の受給者は数える対象が異なる</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>施設の在籍者数と保険者の受給者数を同じものとして比べられない。年報は施設の所在地を問わず当広域連合の被保険者を数え、調査②は保険者を問わず区域内の施設の在籍者を数える。介護老人保健施設だけが在籍206人＞受給134.1人／月であり、他の3区分は受給＞在籍である。</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>在籍と受給を並べるときは数える対象の違いを注記する（10シート）。区域内の定員を必要利用定員総数の上限として扱わない。到達率が100％を超えることは誤りではない（確認事項No.88・No.141）。</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>①の要介護度分布は在宅の認定者の分布と食い違う</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>①の割合を在宅の認定者全体の割合として引けない。χ²＝43.5（自由度6。1％点16.81）で、要介護3が期待の2.8倍、要支援1が期待の0.16倍である。</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>留保No.2の測定値である。代表KPI H12（必要サービス未充足率）も同じ母集団の指標となるため、母集団を明記して用いる（確認事項No.140）。</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>注1）「必須」は、計画本文に数値を載せる際に必ず付す留保である。「決定待ち」は、点検事項の取扱いが決まるまで数値が確定しないものである。注2）本報告書では、「〜に由来する」「〜と整合する（根拠として）」「1件も〜ない」「有意差がないため関係がない」「全国トップ級」の5つの表現を用いない（受託者の自己点検（記述ルール））。注3）点検事項35件の全文は別冊「実施済み3調査の受領点検と集計」02シートによる。</t>
         </is>
@@ -2687,7 +2871,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2699,7 +2883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2841,9 +3025,9 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -2954,7 +3138,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>第2章第4節
+          <t>第2章第5節
 第5章 基本目標2</t>
         </is>
       </c>
@@ -2963,9 +3147,9 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3169,8 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2</t>
+          <t>第2章第4節
+第5章 基本目標2</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2993,9 +3178,9 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -3024,9 +3209,9 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -3297,9 +3482,9 @@
           <t>④のみで記述する</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -3396,62 +3581,85 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="44" customHeight="1">
+    <row r="28" ht="52" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>着手可</t>
+          <t>反映済</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>点検事項の取扱いの決定を要しない。計画素案の第1章第7節・第2章第3節・第2章第4節・第2章第6節・第3章第5節・第5章・第6章第4節・第6章第5節へ反映する。</t>
+          <t>計画素案の本文に反映済みであることを素案の実物で確認したもの。第2章第4節（高齢者の生活実態）は令和8年9月15日に健康とくらしの調査の結果を入れ、4段落・表1から30段落・表8となった。第6章第2節・第4節は令和8年9月16日にサービス見込量の算定 第1次概算の値へ差し替えた。</t>
         </is>
       </c>
       <c r="D28" s="23" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>R8.8〜9</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="44" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>決定待ち</t>
+          <t>反映済</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>着手可</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>点検事項No.1・No.2・No.13・No.25・No.31・No.32の取扱いが決まってから反映する。ヒアリングシート項目13・項目14でご意向を確認する。</t>
+          <t>点検事項の取扱いの決定を要しない。計画素案の第1章第7節・第2章第3節・第2章第6節・第3章第5節・第5章・第6章第5節へ反映する。</t>
         </is>
       </c>
       <c r="D29" s="23" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>決定待ち</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>点検事項No.1・No.2・No.13・No.25・No.31・No.32の取扱いが決まってから反映する。ヒアリングシート項目13・項目14でご意向を確認する。</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
           <t>R8.9</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="39" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>注1）所見20件のうち11件は点検事項の取扱いの決定を要せず着手できる。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。</t>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>注1）所見20件のうち5件は反映済み、6件は点検事項の取扱いの決定を要せず着手できる。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（896段落143表36図）の本文と表を実際に読んで判定している。固定値では書いていない。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A26:F26"/>
   </mergeCells>
@@ -3535,7 +3743,7 @@
           <t>地区を結合キーとする方法が唯一の選択肢であった。</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>前提</t>
         </is>
@@ -3735,7 +3943,7 @@
           <t>調査票の設計の改善点として記録する。調査票の設計は発注者が行うものであり、受託者は提案にとどまる（仕様書４（3））。</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>申し送り</t>
         </is>
@@ -3763,7 +3971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4078,22 +4286,22 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>調査の設計そのものによるものである。母集団が「在宅生活の維持が難しい利用者」であり、区域内の在宅利用者全体ではない。</t>
+          <t>調査の設計そのものによるものであり、留保自体は残る。母集団が「在宅生活の維持が難しい利用者」であり、区域内の在宅利用者全体ではない。ただし令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、偏りの大きさと向きを測定できるようになった。</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>解消できない。第11期に向けて設計の見直しを提案する</t>
+          <t>測定はできた。留保そのものは解消できない。第11期に向けて設計の見直しを提案する</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>「調査対象となった99人のうち」と明記する。H12の20.4％も同じ留保が付く</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>未解消</t>
+          <t>「調査対象となった99人のうち」と明記する。偏りをχ²＝43.5（自由度6。1％点16.81）として示せるようになったため、「課題のある層に偏っている」ではなく「要介護3が期待の2.8倍、要支援1が期待の0.16倍」と書ける。H12の20.4％も同じ留保が付く</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>測定済み</t>
         </is>
       </c>
     </row>
@@ -4257,10 +4465,74 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>注3）留保No.7は本報告書で最も重い留保である。①在宅生活改善調査から算定するH12（20.4％）は第10期の代表KPIに用いる案としているが、母集団が抽出であることを指標の定義に明記する必要がある。注4）本シートは、公表データの取得により報告書作成時点から変わった部分を記録するものである。報告書の本体（02〜13シート）の数値は変更していない。</t>
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>②の在籍者を保険者の受給者と同じものとして扱えない（11シートNo.15）</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>数える対象が異なるため一致しない。年報は施設の所在地を問わず当広域連合の被保険者を数え、調査②は保険者を問わず区域内の施設の在籍者を数える。</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>年報（令和7年度）の要介護度別の明細により区分ごとに受給者数を実数で置けるようになった</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>10シートで在籍と受給を並べ、数える対象の違いを注記した。区域内の定員を必要利用定員総数の上限として扱わない（確認事項No.88・No.141）</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>測定済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>①の代表性を判定できない（11シートNo.3の一部）</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>配布数の記録はないままであるが、回答の構成が母集団と食い違うかどうかは判定できるようになった。</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>年報（令和7年度）の要介護度別の明細と、施設・居住系の要介護度別の差引きによる在宅の認定者の分布</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>χ²検定により代表しないことを示したうえで、「在宅で困難を抱える方の状況」として引く（確認事項No.140）</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>測定済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="78" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>注3）留保No.7は本報告書で最も重い留保である。①在宅生活改善調査から算定するH12（20.4％）は第10期の代表KPIに用いる案としているが、母集団が抽出であることを指標の定義に明記する必要がある。令和8年9月11日に偏りの大きさと向きを測定できるようになったが、留保そのものは解消していない。注4）本シートは、公表データの取得により報告書作成時点から変わった部分を記録するものである。報告書の本体（02〜13シート）の数値のうち、10シートの見込量は令和8年9月16日にサービス見込量の算定 第1次概算の値へ差し替えた（計画素案 第6章と同じ値にするため）。そのほかの数値は変更していない。注5）「測定済み」は、留保そのものは残るが、その大きさと向きを数値で示せるようになったことを表す。</t>
         </is>
       </c>
     </row>
@@ -4268,9 +4540,9 @@
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節・第5章基本目標4の根拠</t>
+          <t>第2章第6節・第5章基本目標4の根拠</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節の根拠</t>
+          <t>第2章第6節の根拠</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節、第5章基本目標4、代表KPI H13・H14</t>
+          <t>第2章第6節、第5章基本目標4、代表KPI H13・H14</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1746,7 +1746,7 @@
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節の基礎数値。訪問系は3事業所分にとどまることを注記する</t>
+          <t>第2章第6節の基礎数値。訪問系は3事業所分にとどまることを注記する</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節では、把握範囲を明記したうえで記述する。本調査を継続する意義を第10期に位置づける</t>
+          <t>第2章第6節では、把握範囲を明記したうえで記述する。本調査を継続する意義を第10期に位置づける</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>第2章第6節
+          <t>第2章第3節
 第6章第5節</t>
         </is>
       </c>
@@ -2965,9 +2965,9 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -2995,9 +2995,9 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -3055,9 +3055,9 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -3086,9 +3086,9 @@
           <t>表現の確認</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節</t>
+          <t>第2章第6節</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3116,9 +3116,9 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節</t>
+          <t>第2章第6節</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節
+          <t>第2章第6節
 第5章 基本目標4</t>
         </is>
       </c>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節</t>
+          <t>第2章第6節</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -3544,9 +3544,9 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>計画素案の本文に反映済みであることを素案の実物で確認したもの。第2章第4節（高齢者の生活実態）は令和8年9月15日に健康とくらしの調査の結果を入れ、4段落・表1から30段落・表8となった。第6章第2節・第4節は令和8年9月16日にサービス見込量の算定 第1次概算の値へ差し替えた。</t>
+          <t>計画素案の本文に反映済みであることを素案の実物で確認したもの。第2章第4節（高齢者の生活実態）は健康とくらしの調査の結果を入れ、4段落・表1から30段落・表8となった。第6章第2節・第4節はサービス見込量の算定 第1次概算の値へ差し替えた。第1章第7節（通常の事業の実施地域）・第2章第3節（運営法人の集中）・第6章第4節（区域内の入居状況と受給者数）・第6章第5節（入所の経路）は、点検事項の決定を要しないものとして反映した。</t>
         </is>
       </c>
       <c r="D28" s="23" t="n"/>
@@ -3610,18 +3610,18 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>点検事項の取扱いの決定を要しない。計画素案の第1章第7節・第2章第3節・第2章第6節・第3章第5節・第5章・第6章第5節へ反映する。</t>
+          <t>点検事項の取扱いの決定を要しないもの。決定を要しないものはすべて反映済みである。</t>
         </is>
       </c>
       <c r="D29" s="23" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち5件は反映済み、6件は点検事項の取扱いの決定を要せず着手できる。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（896段落143表36図）の本文と表を実際に読んで判定している。固定値では書いていない。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（923段落145表36図）の本文と表を章節ごとに読んで判定している。固定値では書いていない。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>18施設・定員652人・入所者536人。新規入所335人の入所前は病院・診療所57.0％・自宅27.5％。退去349人の退去先は病院・診療所47.0％・死亡27.2％。</t>
+          <t>18施設・定員652人・入所者536人（入所欄の合計。記入のない1施設を要介護度別の内訳58人で補うと594人）。新規入所335人の入所前は病院・診療所57.0％・自宅27.5％。退去349人の退去先は病院・診療所47.0％・死亡27.2％。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査で24.3％（n=4,128）。介護保険の給付対象外。</t>
+          <t>健康とくらしの調査の回答者4,128人のうち24.3％（1,002人）。生活動作の困りごとの最上位。介護保険の給付対象外。</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>回答18施設の定員652人・入所者594人（入所率91.1％）。</t>
+          <t>回答18施設の定員652人。入所者は入所欄の合計536人（入所率82.2％）と、入所欄の記入がない1施設を要介護度別の内訳58人で補った594人（入所率91.1％）の2通りがある。どちらを用いるかの決定を要する。</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -3650,7 +3650,7 @@
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（923段落145表36図）の本文と表を章節ごとに読んで判定している。固定値では書いていない。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（925段落145表36図）の本文と表を章節ごとに読んで判定している。固定値では書いていない。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -221,6 +221,9 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -243,9 +246,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -714,7 +714,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>在宅生活の維持が困難72人（72.7％）。必要な生活支援は外出同行51件・見守り34件・通いの場34件。より適切なサービスは小規模多機能44件が最多。</t>
+          <t>在宅生活の維持が困難72人（有効回答98票の73.5％）。必要な生活支援は外出同行51件・見守り34件・通いの場34件。より適切なサービスは小規模多機能44件が最多。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>解消6件・測定済み3件・未解消3件・一部解消1件・公表待ち1件・決定待ち1件。訪問介護13事業所181人の全数把握により、訪問系の代表性の留保が解消した。令和8年9月11日に年報の要介護度別の明細を収めたことにより、調査①の偏りと、在籍と受給の違いを測定できるようになった。</t>
+          <t>解消6件・測定済み3件・未解消3件・一部解消1件・公表待ち1件・決定待ち1件。訪問介護13事業所181人の全数把握により、訪問系の代表性の留保が解消した。年報の要介護度別の明細を確認できたことにより、調査①の偏りと、在籍と受給の違いを測定できるようになった。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1532,7 +1532,7 @@
           <t>グループホーム・特定施設・住宅型有料・サ高住</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="25" t="n">
         <v>116</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1683,7 +1683,7 @@
           <t>計</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="19" t="n">
         <v>43</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -1741,8 +1741,8 @@
           <t>348人</t>
         </is>
       </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="23" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -1761,8 +1761,8 @@
           <t>67.1％</t>
         </is>
       </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="23" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -1781,8 +1781,8 @@
           <t>19.9％</t>
         </is>
       </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="23" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -1801,8 +1801,8 @@
           <t>採用83人・離職65人</t>
         </is>
       </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="23" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="24" t="n"/>
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -1821,8 +1821,8 @@
           <t>37人（13事業所）</t>
         </is>
       </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -1841,8 +1841,8 @@
           <t>42人（13.3％）</t>
         </is>
       </c>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="23" t="n"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="16" t="n">
         <v>206</v>
       </c>
       <c r="C13" s="8" t="n">
@@ -2224,7 +2224,7 @@
           <t>いずれも利用していない</t>
         </is>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="16" t="n">
         <v>486</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -2279,7 +2279,7 @@
           <t>訪問系13事業所のうち美瑛町を実施地域とするのは4事業所である。健康とくらしの調査では自力移動の手段がない層が20％台にある。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="n"/>
+      <c r="D24" s="24" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
           <t>この3サービスは区域内に事業所がなく、受給率も0.0％である。</t>
         </is>
       </c>
-      <c r="D25" s="23" t="n"/>
+      <c r="D25" s="24" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
           <t>老健3施設240人が区域内の中間施設として機能している。在宅への復帰か施設入所かの分岐点が医療機関にある。</t>
         </is>
       </c>
-      <c r="D26" s="23" t="n"/>
+      <c r="D26" s="24" t="n"/>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
           <t>グループホーム7・特定施設3・住宅型有料9・サ高住2・軽費1の22施設が該当する。うち調査に回答したのは一部にとどまる。</t>
         </is>
       </c>
-      <c r="D27" s="23" t="n"/>
+      <c r="D27" s="24" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
           <t>区域内の小規模多機能5事業所はすべて1法人が美瑛町で運営し、東川町・東神楽町を実施地域とするのは1事業所のみである。</t>
         </is>
       </c>
-      <c r="D28" s="23" t="n"/>
+      <c r="D28" s="24" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>「在宅生活の維持が困難72.7％」を区域内の在宅利用者全体の割合と読めない。令和8年9月11日の突合により、偏りの大きさと向きを測定した。要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5、自由度6。1％点16.81）。要介護3は期待6.7人に対し19人（2.8倍）、要支援1は期待18.9人に対し3人（0.16倍）である。</t>
+          <t>「在宅生活の維持が困難73.5％」を区域内の在宅利用者全体の割合と読めない。年報の要介護度別の明細との突合により、偏りの大きさと向きを測定した。要介護度分布は在宅の認定者の分布と食い違う（χ²＝43.5、自由度6。1％点16.81）。要介護3は期待6.7人に対し19人（2.8倍）、要支援1は期待18.9人に対し3人（0.16倍）である。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2605,7 +2605,7 @@
           <t>点検事項No.1の取扱いの決定による。受託者の案は348人（訪問系13人を実数とする）。</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -2630,7 +2630,7 @@
           <t>点検事項No.31の取扱いの決定による。介護サービス情報公表システムの個別画面による確認を提案する。</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -2655,7 +2655,7 @@
           <t>地区別の記述を行わない（13シート）。</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>決定済</t>
         </is>
@@ -2680,7 +2680,7 @@
           <t>点検事項No.2の取扱いの決定による。提出元を除いた集計の併記又は質的な記述を提案する。</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -2705,7 +2705,7 @@
           <t>点検事項No.25。発注者への確認による。</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>留保No.2の測定値である。代表KPI H12（必要サービス未充足率）も同じ母集団の指標となるため、母集団を明記して用いる（確認事項No.140）。</t>
+          <t>留保No.2の測定値である。代表KPI H12（区域内で提供できないサービスが必要と判断された利用者の割合）も同じ母集団の指標となるため、母集団を明記して用いる（確認事項No.140）。</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>利用者票99票のうち在宅生活の維持が困難72人（72.7％）。</t>
+          <t>利用者票99票のうち、この設問の有効回答98票において在宅生活の維持が困難72人（73.5％）。</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -3595,7 +3595,7 @@
           <t>計画素案の本文に反映済みであることを素案の実物で確認したもの。第2章第4節（高齢者の生活実態）は健康とくらしの調査の結果を入れ、4段落・表1から30段落・表8となった。第6章第2節・第4節はサービス見込量の算定 第1次概算の値へ差し替えた。第1章第7節（通常の事業の実施地域）・第2章第3節（運営法人の集中）・第6章第4節（区域内の入居状況と受給者数）・第6章第5節（入所の経路）は、点検事項の決定を要しないものとして反映した。</t>
         </is>
       </c>
-      <c r="D28" s="23" t="n"/>
+      <c r="D28" s="24" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
           <t>点検事項の取扱いの決定を要しないもの。決定を要しないものはすべて反映済みである。</t>
         </is>
       </c>
-      <c r="D29" s="23" t="n"/>
+      <c r="D29" s="24" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
       </c>
     </row>
     <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -3639,7 +3639,7 @@
           <t>点検事項No.1・No.2・No.13・No.25・No.31・No.32の取扱いが決まってから反映する。ヒアリングシート項目13・項目14でご意向を確認する。</t>
         </is>
       </c>
-      <c r="D30" s="23" t="n"/>
+      <c r="D30" s="24" t="n"/>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（925段落145表36図）の本文と表を章節ごとに読んで判定している。固定値では書いていない。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（926段落145表36図）の本文と表を章節ごとに読んで判定している。固定値では書いていない。</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
           <t>①の個票を地区に割り付けられない。①と④を地区で結合できない。</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>障害</t>
         </is>
@@ -3793,7 +3793,7 @@
           <t>②を地区に割り付けられない。</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>障害</t>
         </is>
@@ -3818,7 +3818,7 @@
           <t>③は事業所を経由して町までは割り付けられるが、地区までは割り付けられない。</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>障害</t>
         </is>
@@ -3843,7 +3843,7 @@
           <t>結合できる事業所が少なく、集計に耐えない。</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>障害</t>
         </is>
@@ -3868,7 +3868,7 @@
           <t>本業務では横断クロス集計を行わない。</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>決定</t>
         </is>
@@ -4061,7 +4061,7 @@
           <t>第2章第6節に全数把握の表を追加した</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4093,7 +4093,7 @@
           <t>第2章第6節。住まいの整備方針と訪問介護の供給力が一体であることの根拠</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4125,7 +4125,7 @@
           <t>第2章第6節、第5章 基本目標4</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4157,7 +4157,7 @@
           <t>第2章第1節の世帯の記述を是正した</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4171,17 +4171,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>H12（必要サービス未充足率）のデータ源がない</t>
+          <t>H12（当初の定義「必要サービス未充足率」）のデータ源がない</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>①在宅生活改善調査 問3（本報告書02シート）</t>
+          <t>①在宅生活改善調査（より適切と思われるサービス。本報告書02シート）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>区域内に事業所が存在しない4サービスを「より適切と思われるサービス」として選んだ票は98票中20票（20.4％）である。H12の代理指標として定義できる。</t>
+          <t>区域内に事業所が存在しない4サービスを「より適切と思われるサービス」として選んだ票は99票中20票（20.2％）である。分母はこの設問の有効回答99票である（要介護度の有効回答98票ではない）。H12の代理指標として定義できる。指標名は「区域内で提供できないサービスが必要と判断された利用者の割合」に改める。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -4189,7 +4189,7 @@
           <t>第4章第3節・資料1のH12</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4221,7 +4221,7 @@
           <t>第4章第3節・資料1のH07・H08</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>調査の設計そのものによるものであり、留保自体は残る。母集団が「在宅生活の維持が難しい利用者」であり、区域内の在宅利用者全体ではない。ただし令和8年9月11日に年報（令和7年度）の要介護度別の明細を収めたことにより、偏りの大きさと向きを測定できるようになった。</t>
+          <t>調査の設計そのものによるものであり、留保自体は残る。母集団が「在宅生活の維持が難しい利用者」であり、区域内の在宅利用者全体ではない。ただし年報（令和7年度）の要介護度別の明細を確認できたことにより、偏りの大きさと向きを測定できるようになった。</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -4296,10 +4296,10 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>「調査対象となった99人のうち」と明記する。偏りをχ²＝43.5（自由度6。1％点16.81）として示せるようになったため、「課題のある層に偏っている」ではなく「要介護3が期待の2.8倍、要支援1が期待の0.16倍」と書ける。H12の20.4％も同じ留保が付く</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
+          <t>「調査対象となった99人のうち」と明記する。偏りをχ²＝43.5（自由度6。1％点16.81）として示せるようになったため、「課題のある層に偏っている」ではなく「要介護3が期待の2.8倍、要支援1が期待の0.16倍」と書ける。H12の20.2％も同じ留保が付く</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>測定済み</t>
         </is>
@@ -4331,7 +4331,7 @@
           <t>施設側からみた住替えとして記述する</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>未解消</t>
         </is>
@@ -4427,7 +4427,7 @@
           <t>［要確認］として注記を残す</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>未解消</t>
         </is>
@@ -4491,7 +4491,7 @@
           <t>10シートで在籍と受給を並べ、数える対象の違いを注記した。区域内の定員を必要利用定員総数の上限として扱わない（確認事項No.88・No.141）</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>測定済み</t>
         </is>
@@ -4523,7 +4523,7 @@
           <t>χ²検定により代表しないことを示したうえで、「在宅で困難を抱える方の状況」として引く（確認事項No.140）</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>測定済み</t>
         </is>
@@ -4532,7 +4532,7 @@
     <row r="25" ht="78" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>注3）留保No.7は本報告書で最も重い留保である。①在宅生活改善調査から算定するH12（20.4％）は第10期の代表KPIに用いる案としているが、母集団が抽出であることを指標の定義に明記する必要がある。令和8年9月11日に偏りの大きさと向きを測定できるようになったが、留保そのものは解消していない。注4）本シートは、公表データの取得により報告書作成時点から変わった部分を記録するものである。報告書の本体（02〜13シート）の数値のうち、10シートの見込量は令和8年9月16日にサービス見込量の算定 第1次概算の値へ差し替えた（計画素案 第6章と同じ値にするため）。そのほかの数値は変更していない。注5）「測定済み」は、留保そのものは残るが、その大きさと向きを数値で示せるようになったことを表す。</t>
+          <t>注3）留保No.7は本報告書で最も重い留保である。①在宅生活改善調査から算定するH12（20.2％）は第10期の代表KPIに用いる案としているが、母集団が抽出であることを指標の定義に明記する必要がある。偏りの大きさと向きは測定できるようになったが、留保そのものは解消していない。注4）本シートは、公表データの取得により報告書作成時点から変わった部分を記録するものである。報告書の本体（02〜13シート）の数値のうち、10シートの見込量は令和8年9月16日にサービス見込量の算定 第1次概算の値へ差し替えた（計画素案 第6章と同じ値にするため）。そのほかの数値は変更していない。注5）「測定済み」は、留保そのものは残るが、その大きさと向きを数値で示せるようになったことを表す。</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4917,7 +4917,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>【在宅生活の維持の見通し（99票）】</t>
+          <t>【在宅生活の維持の見通し（有効回答98票）】</t>
         </is>
       </c>
     </row>
@@ -5007,85 +5007,85 @@
       <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="12" t="inlineStr"/>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>無回答</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>回収票99票との差。構成比の分母は有効回答98票である</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>【必要な生活支援（複数回答・99票）】</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>生活支援</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>回答者に対する割合</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>見方</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>外出同行（通院、買い物など）</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>51.5％</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>最多。移動の確保が在宅生活の継続の鍵である。健康とくらしの調査でも自力移動の手段がない層が20％台であることと符合する</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>見守り、声かけ</t>
+          <t>外出同行（通院、買い物など）</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>34.3％</t>
+          <t>51.5％</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>介護保険の給付では担いにくい。生活支援体制整備事業の対象</t>
+          <t>最多。移動の確保が在宅生活の継続の鍵である。健康とくらしの調査でも自力移動の手段がない層が20％台であることと符合する</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>サロンなどの定期的な通いの場</t>
+          <t>見守り、声かけ</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -5100,40 +5100,44 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>通いの場は介護予防だけでなく在宅生活の継続の資源でもある</t>
+          <t>介護保険の給付では担いにくい。生活支援体制整備事業の対象</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>配食</t>
+          <t>サロンなどの定期的な通いの場</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>29.3％</t>
+          <t>34.3％</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="9" t="n"/>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>通いの場は介護予防だけでなく在宅生活の継続の資源でもある</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>掃除・洗濯</t>
+          <t>配食</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>23.2％</t>
+          <t>29.3％</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
@@ -5143,15 +5147,15 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>調理</t>
+          <t>掃除・洗濯</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>21.2％</t>
+          <t>23.2％</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr"/>
@@ -5161,15 +5165,15 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>買い物（宅配は含まない）</t>
+          <t>調理</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>20.2％</t>
+          <t>21.2％</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr"/>
@@ -5179,15 +5183,15 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>ゴミ出し</t>
+          <t>買い物（宅配は含まない）</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>19.2％</t>
+          <t>20.2％</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr"/>
@@ -5197,7 +5201,7 @@
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>移送サービス（介護・福祉ﾀｸｼｰ等）</t>
+          <t>ゴミ出し</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
@@ -5215,15 +5219,15 @@
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>移送サービス（介護・福祉ﾀｸｼｰ等）</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>13.1％</t>
+          <t>19.2％</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr"/>
@@ -5233,116 +5237,112 @@
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>特にない</t>
+          <t>その他</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>6.1％</t>
+          <t>13.1％</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="5" t="inlineStr"/>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>特にない</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>6.1％</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>【より適切と思われるサービス（複数回答・99票）】</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>サービス</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>回答者に対する割合</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>在宅/施設等</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>見方</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>小規模多機能</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>44.4％</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>在宅</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>最多。ただし区域内の小規模多機能5事業所はすべて社会福祉法人美瑛慈光会が美瑛町で運営しており、うち36票が同一法人の2事業所からの提出である（点検事項No.2・08シート）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>住宅型有料</t>
+          <t>小規模多機能</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>27.3％</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>施設等</t>
+          <t>44.4％</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>在宅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>最多。ただし区域内の小規模多機能5事業所はすべて社会福祉法人美瑛慈光会が美瑛町で運営しており、うち36票が同一法人の2事業所からの提出である（点検事項No.2・08シート）</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ</t>
+          <t>住宅型有料</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>20.2％</t>
+          <t>27.3％</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -5356,7 +5356,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特別養護老人ﾎｰﾑ</t>
+          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
@@ -5378,20 +5378,20 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>訪問介護､訪問入浴</t>
+          <t>特別養護老人ﾎｰﾑ</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>18.2％</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>在宅</t>
+          <t>20.2％</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>施設等</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
@@ -5400,15 +5400,15 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ｼｮｰﾄｽﾃｲ</t>
+          <t>訪問介護､訪問入浴</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>16.2％</t>
+          <t>18.2％</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -5422,7 +5422,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>通所介護､通所ﾘﾊ､認知症対応型通所</t>
+          <t>ｼｮｰﾄｽﾃｲ</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
@@ -5444,7 +5444,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ｻ高住</t>
+          <t>通所介護､通所ﾘﾊ､認知症対応型通所</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
@@ -5455,9 +5455,9 @@
           <t>16.2％</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t>施設等</t>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>在宅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
@@ -5466,20 +5466,20 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>訪問看護</t>
+          <t>ｻ高住</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>15.2％</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>在宅</t>
+          <t>16.2％</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>施設等</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
@@ -5488,7 +5488,7 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>介護老人保健施設</t>
+          <t>訪問看護</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
@@ -5499,9 +5499,9 @@
           <t>15.2％</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>施設等</t>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>在宅</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
@@ -5510,20 +5510,20 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>居宅療養管理指導</t>
+          <t>介護老人保健施設</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>14.1％</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>在宅</t>
+          <t>15.2％</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>施設等</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
@@ -5532,15 +5532,15 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>看護小規模多機能</t>
+          <t>居宅療養管理指導</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>10.1％</t>
+          <t>14.1％</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -5549,16 +5549,12 @@
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>区域内に事業所がない（見える化K3q＝0）</t>
-        </is>
-      </c>
+      <c r="F37" s="5" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>軽費老人ﾎｰﾑ</t>
+          <t>看護小規模多機能</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
@@ -5569,52 +5565,52 @@
           <t>10.1％</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
-        <is>
-          <t>施設等</t>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>在宅</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>区域内に事業所がない（見える化K3q＝0）</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>定期巡回ｻｰﾋﾞｽ</t>
+          <t>軽費老人ﾎｰﾑ</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>9.1％</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>在宅</t>
+          <t>10.1％</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>施設等</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>区域内に事業所がない（見える化K3m＝0）</t>
-        </is>
-      </c>
+      <c r="F39" s="5" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>訪問診療</t>
+          <t>定期巡回ｻｰﾋﾞｽ</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>8.1％</t>
+          <t>9.1％</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -5623,20 +5619,24 @@
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>区域内に事業所がない（見える化K3m＝0）</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護</t>
+          <t>訪問診療</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>7.1％</t>
+          <t>8.1％</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -5645,24 +5645,20 @@
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>区域内に事業所がない（見える化K3n＝0）</t>
-        </is>
-      </c>
+      <c r="F41" s="5" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>訪問ﾘﾊ</t>
+          <t>夜間対応型訪問介護</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>6.1％</t>
+          <t>7.1％</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -5671,25 +5667,29 @@
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>区域内に事業所がない（見える化K3n＝0）</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>介護医療院</t>
+          <t>訪問ﾘﾊ</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>3.0％</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>施設等</t>
+          <t>6.1％</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>在宅</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
@@ -5698,15 +5698,15 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>特定施設</t>
+          <t>介護医療院</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>1.0％</t>
+          <t>3.0％</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
@@ -5717,74 +5717,72 @@
       <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="5" t="inlineStr"/>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>1.0％</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>施設等</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>【区域内に事業所がないサービスへの言及】</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>サービス</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>見える化
 事業所数</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>受給率</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>見方</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>夜間対応型訪問介護</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C48" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>0.0％</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>事業所がないため利用できない。利用者票で必要と回答されていることは、第6章第4節（24時間対応サービスの確保方策）の根拠となる</t>
         </is>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型</t>
+          <t>夜間対応型訪問介護</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C49" s="15" t="n">
         <v>0</v>
@@ -5804,11 +5802,11 @@
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>看護小規模多機能型</t>
+          <t>定期巡回・随時対応型</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C50" s="15" t="n">
         <v>0</v>
@@ -5825,93 +5823,99 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>看護小規模多機能型</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>事業所がないため利用できない。利用者票で必要と回答されていることは、第6章第4節（24時間対応サービスの確保方策）の根拠となる</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B51" s="11" t="n">
+      <c r="B52" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr"/>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr"/>
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>延べ26件。実人数は不明（複数回答のため）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>【事業所票15件による居場所の変更（171人）】</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>変更先</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>構成比</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>見方</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>死亡</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>32.7％</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="5" t="inlineStr"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>住宅型有料老人ﾎｰﾑ</t>
+          <t>死亡</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>15.2％</t>
+          <t>32.7％</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr"/>
@@ -5921,15 +5925,15 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>特別養護老人ﾎｰﾑ</t>
+          <t>住宅型有料老人ﾎｰﾑ</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>10.5％</t>
+          <t>15.2％</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr"/>
@@ -5939,15 +5943,15 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>介護老人保健施設</t>
+          <t>特別養護老人ﾎｰﾑ</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>8.8％</t>
+          <t>10.5％</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
@@ -5957,15 +5961,15 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>病院・診療所</t>
+          <t>介護老人保健施設</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>8.2％</t>
+          <t>8.8％</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr"/>
@@ -5975,15 +5979,15 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>病院・診療所（区域外）</t>
+          <t>病院・診療所</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>7.6％</t>
+          <t>8.2％</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr"/>
@@ -5993,15 +5997,15 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>住宅型有料老人ﾎｰﾑ（区域外）</t>
+          <t>病院・診療所（区域外）</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>6.4％</t>
+          <t>7.6％</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr"/>
@@ -6011,15 +6015,15 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>兄弟･子ども･親戚等の家（区域外）</t>
+          <t>住宅型有料老人ﾎｰﾑ（区域外）</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>2.3％</t>
+          <t>6.4％</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
@@ -6029,15 +6033,15 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ</t>
+          <t>兄弟･子ども･親戚等の家（区域外）</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>1.8％</t>
+          <t>2.3％</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr"/>
@@ -6047,7 +6051,7 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>ｻｰﾋﾞｽ付き高齢者向け住宅</t>
+          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
@@ -6065,15 +6069,15 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>地域密着型特別養護老人ﾎｰﾑ</t>
+          <t>ｻｰﾋﾞｽ付き高齢者向け住宅</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>1.2％</t>
+          <t>1.8％</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr"/>
@@ -6083,15 +6087,15 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>その他（区域外）</t>
+          <t>地域密着型特別養護老人ﾎｰﾑ</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>0.6％</t>
+          <t>1.2％</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr"/>
@@ -6101,7 +6105,7 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>特定施設</t>
+          <t>その他（区域外）</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
@@ -6119,7 +6123,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ（区域外）</t>
+          <t>特定施設</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
@@ -6137,7 +6141,7 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>特定施設（区域外）</t>
+          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ（区域外）</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
@@ -6155,7 +6159,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>特別養護老人ﾎｰﾑ（区域外）</t>
+          <t>特定施設（区域外）</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
@@ -6173,7 +6177,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>軽費老人ホーム</t>
+          <t>特別養護老人ﾎｰﾑ（区域外）</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
@@ -6189,52 +6193,70 @@
       <c r="F71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>軽費老人ホーム</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>0.6％</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B72" s="11" t="n">
+      <c r="B73" s="11" t="n">
         <v>171</v>
       </c>
-      <c r="C72" s="11" t="inlineStr">
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>100.0％</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr"/>
-      <c r="E72" s="12" t="inlineStr"/>
-      <c r="F72" s="12" t="inlineStr"/>
-    </row>
-    <row r="74" ht="78" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>注1）利用者票は、事業所が在宅生活の継続に課題があると判断した利用者を抽出して回答する設計である。したがって「在宅生活の維持が困難72.7％」は区域内の在宅利用者全体の割合ではない。計画本文では「調査対象となった99人のうち」と母集団を明記する。注2）「より適切と思われるサービス」は、回答者である事業所が自らの提供するサービスを挙げる構造になっている（点検事項No.2）。小規模多機能44件のうち31件は同一法人の小規模多機能2事業所からの提出票によるものである。計画本文では提出元を除いた集計を併記するか、件数を示さず「事業所からは小規模多機能・住宅型有料・グループホームが挙げられた」と質的に記述する。注3）所在地区の記入形式が統一されていないため、地区別・圏域別の集計は行わない（点検事項No.3・13シート）。</t>
+      <c r="D73" s="12" t="inlineStr"/>
+      <c r="E73" s="12" t="inlineStr"/>
+      <c r="F73" s="12" t="inlineStr"/>
+    </row>
+    <row r="75" ht="104" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>注1）利用者票は、事業所が在宅生活の継続に課題があると判断した利用者を抽出して回答する設計である。したがって「在宅生活の維持が困難73.5％」は区域内の在宅利用者全体の割合ではない。計画本文では「調査対象となった99人のうち」と母集団を明記する。注1-2）割合の分母は設問ごとの有効回答による。在宅生活の維持の見通しは98票（無回答1票）、必要な生活支援及びより適切と思われるサービスは99票である。要介護度の有効回答も98票であるが、これは別の設問の有効回答であって同じ票を指すとは限らない。注2）「より適切と思われるサービス」は、回答者である事業所が自らの提供するサービスを挙げる構造になっている（点検事項No.2）。小規模多機能44件のうち31件は同一法人の小規模多機能2事業所からの提出票によるものである。計画本文では提出元を除いた集計を併記するか、件数を示さず「事業所からは小規模多機能・住宅型有料・グループホームが挙げられた」と質的に記述する。注3）所在地区の記入形式が統一されていないため、地区別・圏域別の集計は行わない（点検事項No.3・13シート）。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A75:F75"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A53:F53"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A10:F10"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D23:E23"/>
     <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6246,7 +6268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6453,204 +6475,201 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>【新規入所者の入所前の居場所（335人）】</t>
+          <t>【入所者数の数え方の照合】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>入所前の居場所</t>
+          <t>種別</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>人数</t>
+          <t>入所欄への記入</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>構成比</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
+          <t>要介護度別内訳の合計</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>補完後（本報告書の採用値）</t>
+        </is>
+      </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>見方</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
+          <t>採用値の用いどころ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>病院・診療所</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>34.9％</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="9" t="n"/>
+          <t>特養・地域密着型特養</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n">
+        <v>88</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>最多。医療機関からの退院が施設入所の主要な経路である。第6章第5節（医療と介護の連携）の根拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
+          <t>入所率（本シート）は補完後、在籍と受給の対照（10シート）は要介護度別内訳</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>病院・診療所（区域外）</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>22.1％</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="9" t="n"/>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>201</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>201</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>最多。医療機関からの退院が施設入所の主要な経路である。第6章第5節（医療と介護の連携）の根拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
+          <t>入所率は入所欄、在籍と受給の対照（10シート）は要介護度別内訳。5人の差は要介護度別内訳のみに計上された分である</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>自宅</t>
+          <t>グループホーム</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>15.5％</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="9" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>在宅からの直接入所。第2章第4節と接続する</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
+          <t>いずれも同じ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>自宅（区域外）</t>
+          <t>特定施設</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>11.9％</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="9" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>在宅からの直接入所。第2章第4節と接続する</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
+          <t>いずれも同じ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>他の施設・住まい等</t>
+          <t>住宅型有料・サ高住</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>8.7％</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>他の施設・住まい等（区域外）</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>6.9％</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>335</v>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>100.0％</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr"/>
-      <c r="F21" s="12" t="inlineStr"/>
+        <v>115</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>いずれも同じ。介護保険の給付の対象外である</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>536</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>599</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>594</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>入所欄の合計536人・要介護度別内訳の合計599人・補完後594人の3通りがある</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>注）「入所者」「在籍」の語で3通りの数が現れるため、本表で対照する。①入所欄への記入は施設が入所者数の欄に記入した人数であり、特養1施設が未記入である。②要介護度別内訳の合計は要介護度別の人数の和であり、未記入の施設も内訳は記入している。③補完後は①に当該施設の内訳58人を加えたものである。介護老人保健施設は①201人・②206人で5人の差があり、要介護度別の内訳のみに計上された分である。要介護度別に扱う集計（10シートの在籍と受給の対照、居所変更実態調査の要介護度構成）は②による。</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>【種別ごとの区域内・区域外の別（新規入所）】</t>
+          <t>【新規入所者の入所前の居場所（335人）】</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>種別</t>
+          <t>入所前の居場所</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>区域内</t>
+          <t>人数</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>区域外</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>区域外の割合</t>
-        </is>
-      </c>
+          <t>構成比</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -6658,447 +6677,631 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
+    <row r="25" ht="24" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>病院・診療所</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>34.9％</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>最多。医療機関からの退院が施設入所の主要な経路である。第6章第5節（医療と介護の連携）の根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>病院・診療所（区域外）</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>22.1％</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>最多。医療機関からの退院が施設入所の主要な経路である。第6章第5節（医療と介護の連携）の根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>自宅</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>15.5％</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>在宅からの直接入所。第2章第4節と接続する</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>自宅（区域外）</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>11.9％</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>在宅からの直接入所。第2章第4節と接続する</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>他の施設・住まい等</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>8.7％</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>他の施設・住まい等（区域外）</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>6.9％</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>335</v>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>100.0％</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr"/>
+      <c r="E31" s="12" t="inlineStr"/>
+      <c r="F31" s="12" t="inlineStr"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>【種別ごとの区域内・区域外の別（新規入所）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>区域内</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>区域外</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>区域外の割合</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>グループホーム</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C35" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>100.0％</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>区域外からの入所が大半を占める。住所地特例により保険者は従前の市町村のままとなる。区域内の定員が区域内の被保険者のために使われているとは限らない</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>住宅型有料・サ高住</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C36" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>100.0％</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B37" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C37" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>100.0％</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>特定施設</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C38" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>100.0％</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>区域外からの入所が大半を占める。住所地特例により保険者は従前の市町村のままとなる。区域内の定員が区域内の被保険者のために使われているとは限らない</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>特養・地域密着型特養</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C39" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>100.0％</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>【未回答の特定施設を公表データで補った場合】</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>調査（2施設）</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>公表データ
 （さわやか東神楽館）</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>定員に対する割合</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>見方</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>定員</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B43" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C43" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D43" s="8" t="n">
         <v>158</v>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>101.3％</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>入居者</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B44" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C44" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D44" s="8" t="n">
         <v>154</v>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>98.7％</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>入居率</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>98.3％</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>100.0％</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>98.7％</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F45" s="17" t="inlineStr">
         <is>
           <t>特定施設は区域内でほぼ満室である。居住系の定員に余裕があるという見方は、個々の施設の空きを意味しない</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>【さわやか東神楽館の入居者の要介護度（97人）】</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>要介護度</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>構成比</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>見方</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>要支援1</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n">
+      <c r="B49" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>19.6％</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>要支援2</t>
         </is>
       </c>
-      <c r="B40" s="8" t="n">
+      <c r="B50" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>7.2％</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>要介護1</t>
         </is>
       </c>
-      <c r="B41" s="8" t="n">
+      <c r="B51" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>43.3％</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>単独で最多。認定者全体で要介護1に集中していることと同じ方向</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>要介護2</t>
         </is>
       </c>
-      <c r="B42" s="8" t="n">
+      <c r="B52" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>12.4％</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>要介護3</t>
         </is>
       </c>
-      <c r="B43" s="8" t="n">
+      <c r="B53" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>8.2％</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>要介護4</t>
         </is>
       </c>
-      <c r="B44" s="8" t="n">
+      <c r="B54" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>7.2％</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>要介護5</t>
         </is>
       </c>
-      <c r="B45" s="8" t="n">
+      <c r="B55" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>2.1％</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46" ht="40" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>要支援1〜要介護1</t>
         </is>
       </c>
-      <c r="B46" s="17" t="n">
+      <c r="B56" s="18" t="n">
         <v>68</v>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>70.1％</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr"/>
-      <c r="E46" s="12" t="inlineStr"/>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr"/>
+      <c r="E56" s="12" t="inlineStr"/>
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>【参考】本施設では軽度者が7割を占める。特定施設が重度者の受け皿として機能しているとは限らない。要支援者が26人入居しており、居住系の見込量を要介護度別に置く際に要支援を無視できない。1施設の値であり、区域内3施設の構成を示すものではない</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="78" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="58" ht="78" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>注1）本調査に回答したのは18施設であり、区域内の施設・住まい31施設のうち13施設が未回答である（把握率58.1％。06シート）。とくに区域内最大の特定施設（さわやか東神楽館・定員100人）が回答していないため、入所前の居場所・退去先の集計は定員56人分の2施設に基づく（点検事項No.32）。定員・入居者数・要介護度別の内訳・従業者数は介護サービス情報公表システムの個別画面（記入日 令和7年10月6日）により補うことができるが、入所前の居場所と退去先は公表されていない。注2）入所率は調査に回答した施設の定員に対するものである。区域内の定員は北海道の名簿による（06シート）。注3）区域内・区域外の別は、調査票の「市内／市外」の選択肢による。「市内」が町単位か広域連合単位かが定義されていないため、介護サービス自給率（δ）との接続には確認を要する（点検事項No.25）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="E26"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="E25"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D45:E45"/>
+  <mergeCells count="32">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="E16"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="E37"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="E18"/>
+    <mergeCell ref="D49:E49"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="D27:E27"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="E39"/>
+    <mergeCell ref="E17"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="E29"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="E28"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="E27"/>
+    <mergeCell ref="E35"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="E38"/>
+    <mergeCell ref="E19"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="E15"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="E36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7243,7 +7446,7 @@
       <c r="B9" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>348</v>
       </c>
       <c r="D9" s="12" t="inlineStr"/>
@@ -7354,7 +7557,7 @@
       <c r="F16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>無回答・無効</t>
         </is>
@@ -7460,7 +7663,7 @@
       <c r="F24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>無回答・無効</t>
         </is>
@@ -7559,7 +7762,7 @@
       <c r="F31" s="5" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>無回答・無効</t>
         </is>
@@ -7872,7 +8075,7 @@
       <c r="F51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="19" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>無回答・無効</t>
         </is>
@@ -8683,15 +8886,15 @@
       <c r="B11" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>717</v>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>14施設・531人</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>+186人</t>
         </is>
@@ -8834,15 +9037,15 @@
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="19" t="n">
         <v>339</v>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>4施設・121人</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>+218</t>
         </is>
@@ -8902,7 +9105,7 @@
       <c r="C22" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -8926,7 +9129,7 @@
       <c r="C23" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -8970,7 +9173,7 @@
       <c r="C25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -8990,7 +9193,7 @@
       <c r="C26" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -9014,7 +9217,7 @@
       <c r="C27" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -9038,7 +9241,7 @@
       <c r="C28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -9377,13 +9580,13 @@
       <c r="B5" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="22" t="n">
         <v>6</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -9401,13 +9604,13 @@
       <c r="B6" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="22" t="n">
         <v>5</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -9428,7 +9631,7 @@
       <c r="C7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="14" t="n">
@@ -9449,13 +9652,13 @@
       <c r="B8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -9473,13 +9676,13 @@
       <c r="B9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -9497,13 +9700,13 @@
       <c r="B10" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="22" t="n">
         <v>8</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -9521,13 +9724,13 @@
       <c r="B11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="22" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="22" t="n">
         <v>5</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -10230,7 +10433,7 @@
           <t>区域内の小規模多機能5事業所はすべて社会福祉法人美瑛慈光会が美瑛町で運営している。小規模多機能の利用者票が同一法人に集中するのは必然である。</t>
         </is>
       </c>
-      <c r="D27" s="23" t="n"/>
+      <c r="D27" s="24" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -10250,7 +10453,7 @@
           <t>回答者である事業所が自らの提供するサービスを挙げる構造がある。</t>
         </is>
       </c>
-      <c r="D28" s="23" t="n"/>
+      <c r="D28" s="24" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -10270,7 +10473,7 @@
           <t>小規模多機能は地域密着型サービスであり、実施地域外の利用は想定されていない。東川町・東神楽町では選択肢が実質的に1つである。</t>
         </is>
       </c>
-      <c r="D29" s="23" t="n"/>
+      <c r="D29" s="24" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="5" t="inlineStr">
         <is>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -220,6 +220,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -244,7 +245,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -642,10 +642,11 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>業務仕様書４（3）が定める4調査の集計・分析の結果をまとめる。①②③は令和8年8月4日に第10期分を受領し、④は令和8年7月に個票データを受領した。4調査を横断したクロス集計は、利用者票の所在地区の記入形式が統一されておらず個票を地区に割り付けられないため、発注者のご意向により行わないこととし、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続する（13シート）。作成日：令和8年8月5日。</t>
-        </is>
-      </c>
-    </row>
+          <t>業務仕様書４（3）が定める4調査の集計・分析の結果をまとめる。①②③は令和8年8月4日に第10期分を受領し、④は令和8年7月に個票データを受領した。4調査を横断したクロス集計は、利用者票の所在地区の記入形式が統一されておらず個票を地区に割り付けられないため、発注者のご意向により行わないこととし、各調査内のクロス集計と公表データによる供給構造の分析により調査相互を接続する（13シート）。初版作成日：令和8年8月5日／最終更新日：令和8年9月25日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -764,7 +765,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>介護職員348人（重複を除く）。介護福祉士67.1％、勤続1年未満19.9％、外国人職員11.6％。令和6年度の採用83人・離職65人。</t>
+          <t>介護職員348人（重複を除く）。介護福祉士67.1％、勤続1年未満19.9％、外国人職員は施設・通所系の介護職員319人の11.6％。令和6年度の採用83人・離職65人。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1014,7 +1015,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>解消6件・測定済み3件・未解消3件・一部解消1件・公表待ち1件・決定待ち1件。訪問介護13事業所181人の全数把握により、訪問系の代表性の留保が解消した。年報の要介護度別の明細を確認できたことにより、調査①の偏りと、在籍と受給の違いを測定できるようになった。</t>
+          <t>解消6件・測定済み3件・未解消2件・一部解消1件・公表待ち1件・決定待ち1件。訪問介護13事業所181人の全数把握により、訪問系の代表性の留保が解消した。年報の要介護度別の明細を確認できたことにより、調査①の偏りと、在籍と受給の違いを測定できるようになった。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1023,6 +1024,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -1165,10 +1167,11 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="78" customHeight="1">
+    <row r="26"/>
+    <row r="27" ht="104" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>注1）本報告書は受託者による集計・分析の結果であり、計画本文への反映は発注者のご意向を確認したうえで行う。注2）個票データ（在宅生活改善調査の利用者票99票、介護人材実態調査の職員個票317人、健康とくらしの調査の個票4,729票）は個人情報を含むため、成果品には集計値のみを収録する。注3）本報告書の点検の詳細は別冊「実施済み3調査の受領点検と集計」（16シート）による。④の詳細は別冊「調査クロス集計・分析」（24シート）による。注4）本報告書は令和8年8月5日現在である。点検事項の取扱いの決定により数値が変わる箇所は11シート及び12シートに示す。</t>
+          <t>注1）本報告書は受託者による集計・分析の結果であり、計画本文への反映は発注者のご意向を確認したうえで行う。注2）個票データ（在宅生活改善調査の利用者票99票、介護人材実態調査の職員個票317人、健康とくらしの調査の個票4,729票）は個人情報を含むため、成果品には集計値のみを収録する。注3）本報告書の点検の詳細は別冊「実施済み3調査の受領点検と集計」（16シート）による。④の詳細は別冊「調査クロス集計・分析」（24シート）による。注4）本報告書は初版を令和8年8月5日に作成し、令和8年9月25日に更新した。見込量は計画素案 第6章（サービス見込量の算定 第1次概算。令和8年9月16日）と同じ値であり、10シートの在籍と受給の対照及び11シートの留保は年報（令和7年度）の要介護度別の明細により更新している。点検事項の取扱いの決定により数値が変わる箇所は11シート及び12シートに示す。</t>
         </is>
       </c>
     </row>
@@ -1213,6 +1216,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1495,6 +1499,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -1592,6 +1597,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
@@ -1683,7 +1689,7 @@
           <t>計</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="20" t="n">
         <v>43</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -1703,6 +1709,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
@@ -1741,8 +1748,8 @@
           <t>348人</t>
         </is>
       </c>
-      <c r="C30" s="24" t="n"/>
-      <c r="D30" s="24" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -1761,8 +1768,8 @@
           <t>67.1％</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -1781,12 +1788,12 @@
           <t>19.9％</t>
         </is>
       </c>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>定着の指標。代表KPI H14の基礎</t>
+          <t>定着の**補足指標**。代表KPI H14は「採用率と離職率の差」であり、本値はH14そのものではない</t>
         </is>
       </c>
     </row>
@@ -1801,8 +1808,8 @@
           <t>採用83人・離職65人</t>
         </is>
       </c>
-      <c r="C33" s="24" t="n"/>
-      <c r="D33" s="24" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -1821,12 +1828,12 @@
           <t>37人（13事業所）</t>
         </is>
       </c>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="24" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>介護職員の10.6％。第5章基本目標4の外国人材の受入れの根拠</t>
+          <t>施設・通所系の介護職員319人の11.6％。第5章基本目標4の外国人材の受入れの根拠</t>
         </is>
       </c>
     </row>
@@ -1841,8 +1848,8 @@
           <t>42人（13.3％）</t>
         </is>
       </c>
-      <c r="C35" s="24" t="n"/>
-      <c r="D35" s="24" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -1850,6 +1857,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37" ht="65" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
@@ -1908,6 +1916,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1995,6 +2004,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
@@ -2105,7 +2115,7 @@
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>206</v>
       </c>
       <c r="C13" s="8" t="n">
@@ -2121,6 +2131,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2224,7 +2235,7 @@
           <t>いずれも利用していない</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>486</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -2240,6 +2251,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
@@ -2279,7 +2291,7 @@
           <t>訪問系13事業所のうち美瑛町を実施地域とするのは4事業所である。健康とくらしの調査では自力移動の手段がない層が20％台にある。</t>
         </is>
       </c>
-      <c r="D24" s="24" t="n"/>
+      <c r="D24" s="16" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -2299,7 +2311,7 @@
           <t>この3サービスは区域内に事業所がなく、受給率も0.0％である。</t>
         </is>
       </c>
-      <c r="D25" s="24" t="n"/>
+      <c r="D25" s="16" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -2319,7 +2331,7 @@
           <t>老健3施設240人が区域内の中間施設として機能している。在宅への復帰か施設入所かの分岐点が医療機関にある。</t>
         </is>
       </c>
-      <c r="D26" s="24" t="n"/>
+      <c r="D26" s="16" t="n"/>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -2339,7 +2351,7 @@
           <t>グループホーム7・特定施設3・住宅型有料9・サ高住2・軽費1の22施設が該当する。うち調査に回答したのは一部にとどまる。</t>
         </is>
       </c>
-      <c r="D27" s="24" t="n"/>
+      <c r="D27" s="16" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -2359,7 +2371,7 @@
           <t>区域内の小規模多機能5事業所はすべて1法人が美瑛町で運営し、東川町・東神楽町を実施地域とするのは1事業所のみである。</t>
         </is>
       </c>
-      <c r="D28" s="24" t="n"/>
+      <c r="D28" s="16" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -2367,6 +2379,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="130" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
@@ -2434,6 +2447,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2605,7 +2619,7 @@
           <t>点検事項No.1の取扱いの決定による。受託者の案は348人（訪問系13人を実数とする）。</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -2630,7 +2644,7 @@
           <t>点検事項No.31の取扱いの決定による。介護サービス情報公表システムの個別画面による確認を提案する。</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -2655,7 +2669,7 @@
           <t>地区別の記述を行わない（13シート）。</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>決定済</t>
         </is>
@@ -2680,7 +2694,7 @@
           <t>点検事項No.2の取扱いの決定による。提出元を除いた集計の併記又は質的な記述を提案する。</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -2705,7 +2719,7 @@
           <t>点検事項No.25。発注者への確認による。</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -2861,6 +2875,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -2908,6 +2923,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3525,12 +3541,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>特定施設は区域内でほぼ満室である</t>
+          <t>特定施設は施設ごとにみると高い入居率である</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>定員156人に対し入居者154人（98.7％）。調査の2施設は入居率98.3％、さわやか東神楽館は100.0％である。</t>
+          <t>調査に回答した2施設は98.3％（令和7年4月1日現在）、未回答の1施設は公表データで97.0％（令和7年10月6日現在）である。時点が異なるため、区域内合計の入居率（定員156人に対し入居者154人・98.7％）は参考値である。</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -3550,6 +3566,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
@@ -3595,7 +3612,7 @@
           <t>計画素案の本文に反映済みであることを素案の実物で確認したもの。第2章第4節（高齢者の生活実態）は健康とくらしの調査の結果を入れ、4段落・表1から30段落・表8となった。第6章第2節・第4節はサービス見込量の算定 第1次概算の値へ差し替えた。第1章第7節（通常の事業の実施地域）・第2章第3節（運営法人の集中）・第6章第4節（区域内の入居状況と受給者数）・第6章第5節（入所の経路）は、点検事項の決定を要しないものとして反映した。</t>
         </is>
       </c>
-      <c r="D28" s="24" t="n"/>
+      <c r="D28" s="16" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
@@ -3617,7 +3634,7 @@
           <t>点検事項の取扱いの決定を要しないもの。決定を要しないものはすべて反映済みである。</t>
         </is>
       </c>
-      <c r="D29" s="24" t="n"/>
+      <c r="D29" s="16" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
@@ -3626,7 +3643,7 @@
       </c>
     </row>
     <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -3639,7 +3656,7 @@
           <t>点検事項No.1・No.2・No.13・No.25・No.31・No.32の取扱いが決まってから反映する。ヒアリングシート項目13・項目14でご意向を確認する。</t>
         </is>
       </c>
-      <c r="D30" s="24" t="n"/>
+      <c r="D30" s="16" t="n"/>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
@@ -3647,6 +3664,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
@@ -3697,6 +3715,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3768,7 +3787,7 @@
           <t>①の個票を地区に割り付けられない。①と④を地区で結合できない。</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>障害</t>
         </is>
@@ -3793,7 +3812,7 @@
           <t>②を地区に割り付けられない。</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>障害</t>
         </is>
@@ -3818,7 +3837,7 @@
           <t>③は事業所を経由して町までは割り付けられるが、地区までは割り付けられない。</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>障害</t>
         </is>
@@ -3843,7 +3862,7 @@
           <t>結合できる事業所が少なく、集計に耐えない。</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>障害</t>
         </is>
@@ -3868,7 +3887,7 @@
           <t>本業務では横断クロス集計を行わない。</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>決定</t>
         </is>
@@ -3949,6 +3968,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="65" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
@@ -3996,6 +4016,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -4061,7 +4082,7 @@
           <t>第2章第6節に全数把握の表を追加した</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4093,7 +4114,7 @@
           <t>第2章第6節。住まいの整備方針と訪問介護の供給力が一体であることの根拠</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4125,7 +4146,7 @@
           <t>第2章第6節、第5章 基本目標4</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4157,7 +4178,7 @@
           <t>第2章第1節の世帯の記述を是正した</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4189,7 +4210,7 @@
           <t>第4章第3節・資料1のH12</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4221,7 +4242,7 @@
           <t>第4章第3節・資料1のH07・H08</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>解消</t>
         </is>
@@ -4234,6 +4255,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
@@ -4299,7 +4321,7 @@
           <t>「調査対象となった99人のうち」と明記する。偏りをχ²＝43.5（自由度6。1％点16.81）として示せるようになったため、「課題のある層に偏っている」ではなく「要介護3が期待の2.8倍、要支援1が期待の0.16倍」と書ける。H12の20.2％も同じ留保が付く</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>測定済み</t>
         </is>
@@ -4331,7 +4353,7 @@
           <t>施設側からみた住替えとして記述する</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>未解消</t>
         </is>
@@ -4427,7 +4449,7 @@
           <t>［要確認］として注記を残す</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>未解消</t>
         </is>
@@ -4491,7 +4513,7 @@
           <t>10シートで在籍と受給を並べ、数える対象の違いを注記した。区域内の定員を必要利用定員総数の上限として扱わない（確認事項No.88・No.141）</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>測定済み</t>
         </is>
@@ -4523,12 +4545,13 @@
           <t>χ²検定により代表しないことを示したうえで、「在宅で困難を抱える方の状況」として引く（確認事項No.140）</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>測定済み</t>
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="78" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
@@ -4579,6 +4602,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4867,6 +4891,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -4889,7 +4914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4914,6 +4939,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -5029,6 +5055,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -5270,6 +5297,7 @@
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="5" t="inlineStr"/>
     </row>
+    <row r="24"/>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
@@ -5739,6 +5767,7 @@
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr"/>
     </row>
+    <row r="46"/>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
@@ -5847,7 +5876,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
+    <row r="52" ht="32" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
           <t>計</t>
@@ -5869,215 +5898,202 @@
       <c r="E52" s="12" t="inlineStr"/>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>延べ26件。実人数は不明（複数回答のため）</t>
-        </is>
-      </c>
-    </row>
+          <t>延べ26件。上記3サービスの選択件数の合計であり、実人数ではない（複数回答のため）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>【事業所票15件による居場所の変更（171人）】</t>
+          <t>【代表KPI H12の算定】</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>変更先</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>人数</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>構成比</t>
-        </is>
-      </c>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr"/>
       <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>指標名</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>区域内で提供できないサービスが必要と判断された利用者の割合</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>当初の定義「必要サービス未充足率」の代理指標として新たに定義したもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>対象とする4サービス</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>4区分</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="n"/>
+      <c r="D57" s="16" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護・定期巡回・随時対応型訪問介護看護・看護小規模多機能型居宅介護・介護医療院。いずれも区域内に事業所が存在しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>分子</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>20票</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="n"/>
+      <c r="D58" s="16" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>4サービスのいずれかを「より適切と思われるサービス」として挙げた実人数。**複数を選んでいても1人1票として数える**（延べ件数ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>分母</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>99票</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="n"/>
+      <c r="D59" s="16" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>当該設問の有効回答。要介護度の有効回答98票ではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>基準値</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>20.2％</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="n"/>
+      <c r="D60" s="16" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>母集団</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>課題事例の抽出</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n"/>
+      <c r="D61" s="16" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>事業所が在宅生活の継続に課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の未充足率ではない（11シートNo.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>【事業所票15件による居場所の変更（171人）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>変更先</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>構成比</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
           <t>見方</t>
         </is>
       </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>死亡</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>32.7％</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>住宅型有料老人ﾎｰﾑ</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>15.2％</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>特別養護老人ﾎｰﾑ</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>10.5％</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>介護老人保健施設</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>8.8％</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>病院・診療所</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>8.2％</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="5" t="inlineStr"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>病院・診療所（区域外）</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>7.6％</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr"/>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="5" t="inlineStr"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>住宅型有料老人ﾎｰﾑ（区域外）</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="C62" s="8" t="inlineStr">
-        <is>
-          <t>6.4％</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="5" t="inlineStr"/>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>兄弟･子ども･親戚等の家（区域外）</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>2.3％</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr"/>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="5" t="inlineStr"/>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>1.8％</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>ｻｰﾋﾞｽ付き高齢者向け住宅</t>
+          <t>死亡</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>1.8％</t>
+          <t>32.7％</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr"/>
@@ -6087,15 +6103,15 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>地域密着型特別養護老人ﾎｰﾑ</t>
+          <t>住宅型有料老人ﾎｰﾑ</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>1.2％</t>
+          <t>15.2％</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr"/>
@@ -6105,15 +6121,15 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>その他（区域外）</t>
+          <t>特別養護老人ﾎｰﾑ</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>0.6％</t>
+          <t>10.5％</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr"/>
@@ -6123,15 +6139,15 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>特定施設</t>
+          <t>介護老人保健施設</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>0.6％</t>
+          <t>8.8％</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr"/>
@@ -6141,15 +6157,15 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ（区域外）</t>
+          <t>病院・診療所</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>0.6％</t>
+          <t>8.2％</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr"/>
@@ -6159,15 +6175,15 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>特定施設（区域外）</t>
+          <t>病院・診療所（区域外）</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>0.6％</t>
+          <t>7.6％</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr"/>
@@ -6177,15 +6193,15 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>特別養護老人ﾎｰﾑ（区域外）</t>
+          <t>住宅型有料老人ﾎｰﾑ（区域外）</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>0.6％</t>
+          <t>6.4％</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr"/>
@@ -6195,15 +6211,15 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>軽費老人ホーム</t>
+          <t>兄弟･子ども･親戚等の家（区域外）</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>0.6％</t>
+          <t>2.3％</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr"/>
@@ -6211,48 +6227,218 @@
       <c r="F72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>1.8％</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr"/>
+      <c r="F73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>ｻｰﾋﾞｽ付き高齢者向け住宅</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>1.8％</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr"/>
+      <c r="E74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型特別養護老人ﾎｰﾑ</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>1.2％</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr"/>
+      <c r="E75" s="5" t="inlineStr"/>
+      <c r="F75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>その他（区域外）</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>0.6％</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr"/>
+      <c r="F76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>0.6％</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ（区域外）</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>0.6％</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>特定施設（区域外）</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>0.6％</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ﾎｰﾑ（区域外）</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>0.6％</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>軽費老人ホーム</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>0.6％</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B73" s="11" t="n">
+      <c r="B82" s="11" t="n">
         <v>171</v>
       </c>
-      <c r="C73" s="11" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>100.0％</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr"/>
-      <c r="E73" s="12" t="inlineStr"/>
-      <c r="F73" s="12" t="inlineStr"/>
-    </row>
-    <row r="75" ht="104" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
+      <c r="D82" s="12" t="inlineStr"/>
+      <c r="E82" s="12" t="inlineStr"/>
+      <c r="F82" s="12" t="inlineStr"/>
+    </row>
+    <row r="83"/>
+    <row r="84" ht="104" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>注1）利用者票は、事業所が在宅生活の継続に課題があると判断した利用者を抽出して回答する設計である。したがって「在宅生活の維持が困難73.5％」は区域内の在宅利用者全体の割合ではない。計画本文では「調査対象となった99人のうち」と母集団を明記する。注1-2）割合の分母は設問ごとの有効回答による。在宅生活の維持の見通しは98票（無回答1票）、必要な生活支援及びより適切と思われるサービスは99票である。要介護度の有効回答も98票であるが、これは別の設問の有効回答であって同じ票を指すとは限らない。注2）「より適切と思われるサービス」は、回答者である事業所が自らの提供するサービスを挙げる構造になっている（点検事項No.2）。小規模多機能44件のうち31件は同一法人の小規模多機能2事業所からの提出票によるものである。計画本文では提出元を除いた集計を併記するか、件数を示さず「事業所からは小規模多機能・住宅型有料・グループホームが挙げられた」と質的に記述する。注3）所在地区の記入形式が統一されていないため、地区別・圏域別の集計は行わない（点検事項No.3・13シート）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="27">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A84:F84"/>
     <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A75:F75"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B59:E59"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A63:F63"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B56:E56"/>
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B58:E58"/>
     <mergeCell ref="D18:E18"/>
+    <mergeCell ref="B60:E60"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B57:E57"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D14:E14"/>
@@ -6268,7 +6454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6293,6 +6479,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -6472,6 +6659,7 @@
       </c>
       <c r="F11" s="12" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -6513,7 +6701,7 @@
           <t>特養・地域密着型特養</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>88</v>
       </c>
       <c r="C15" s="8" t="n">
@@ -6535,7 +6723,7 @@
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>201</v>
       </c>
       <c r="C16" s="8" t="n">
@@ -6646,6 +6834,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
@@ -6819,6 +7008,7 @@
       <c r="E31" s="12" t="inlineStr"/>
       <c r="F31" s="12" t="inlineStr"/>
     </row>
+    <row r="32"/>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
@@ -6962,6 +7152,7 @@
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="5" t="inlineStr"/>
     </row>
+    <row r="40"/>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
@@ -6977,13 +7168,15 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>調査（2施設）</t>
+          <t>調査（2施設）
+令和7年4月1日現在</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
           <t>公表データ
-（さわやか東神楽館）</t>
+（さわやか東神楽館）
+令和7年10月6日現在</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -6993,7 +7186,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>定員に対する割合</t>
+          <t>北海道の名簿による定員</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -7002,7 +7195,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1">
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
           <t>定員</t>
@@ -7017,12 +7210,14 @@
       <c r="D43" s="8" t="n">
         <v>158</v>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>101.3％</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr"/>
+      <c r="E43" s="17" t="n">
+        <v>156</v>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>調査の自己申告の合計は158人で、北海道の名簿による区域内3施設の定員156人と+2人ちがう（有料老人ホームゆうが調査22人・名簿20人）</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -7041,12 +7236,12 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>98.7％</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
     </row>
-    <row r="45" ht="32" customHeight="1">
+    <row r="45" ht="44" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>入居率</t>
@@ -7059,86 +7254,76 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>100.0％</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>98.7％</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>特定施設は区域内でほぼ満室である。居住系の定員に余裕があるという見方は、個々の施設の空きを意味しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+          <t>97.0％</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>97.5％（参考）</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>98.7％（参考）</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>施設ごとにみるといずれも高い入居率である。計の欄は時点の異なる値を合算した参考値であり、区域内の入居率の確定値としては用いない</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="65" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>注）調査に回答した2施設は令和7年4月1日現在、未回答の1施設は介護サービス情報公表システムの令和7年10月6日現在の公表値である。同システムの「入居率」の欄は100.0％と表示されているが、同じ画面の入居者数（男25人・女72人。要介護度別の和も同数）は97人であり、定員100人に対して97.0％となる。公表資料の中で食い違っているため、本報告書では入居者数から計算した97.0％を用いる（点検事項No.32）。時点が異なるため、両者を足した入居率は参考値である。分母を調査の自己申告の合計158人とすると97.5％、北海道の名簿による区域内定員156人とすると98.7％となる。居住系の定員に余裕があるという見方は、個々の施設の空きを意味しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>【さわやか東神楽館の入居者の要介護度（97人）】</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>要介護度</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>構成比</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>見方</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>要支援1</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>19.6％</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="9" t="n"/>
-      <c r="F49" s="5" t="inlineStr"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>要支援2</t>
+          <t>要支援1</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>7.2％</t>
+          <t>19.6％</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
@@ -7148,55 +7333,55 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>要介護1</t>
+          <t>要支援2</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>43.3％</t>
+          <t>7.2％</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr"/>
       <c r="E51" s="9" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>単独で最多。認定者全体で要介護1に集中していることと同じ方向</t>
-        </is>
-      </c>
+      <c r="F51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>要介護2</t>
+          <t>要介護1</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>12.4％</t>
+          <t>43.3％</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
       <c r="E52" s="9" t="n"/>
-      <c r="F52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>単独で最多。認定者全体で要介護1に集中していることと同じ方向</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>要介護3</t>
+          <t>要介護2</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>8.2％</t>
+          <t>12.4％</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr"/>
@@ -7206,15 +7391,15 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>要介護4</t>
+          <t>要介護3</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>7.2％</t>
+          <t>8.2％</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
@@ -7224,62 +7409,80 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>要介護5</t>
+          <t>要介護4</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>2.1％</t>
+          <t>7.2％</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr"/>
       <c r="E55" s="9" t="n"/>
       <c r="F55" s="5" t="inlineStr"/>
     </row>
-    <row r="56" ht="40" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>2.1％</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>要支援1〜要介護1</t>
         </is>
       </c>
-      <c r="B56" s="18" t="n">
+      <c r="B57" s="19" t="n">
         <v>68</v>
       </c>
-      <c r="C56" s="11" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>70.1％</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr"/>
-      <c r="E56" s="12" t="inlineStr"/>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr"/>
+      <c r="E57" s="12" t="inlineStr"/>
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>【参考】本施設では軽度者が7割を占める。特定施設が重度者の受け皿として機能しているとは限らない。要支援者が26人入居しており、居住系の見込量を要介護度別に置く際に要支援を無視できない。1施設の値であり、区域内3施設の構成を示すものではない</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="78" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
+    <row r="58"/>
+    <row r="59" ht="78" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>注1）本調査に回答したのは18施設であり、区域内の施設・住まい31施設のうち13施設が未回答である（把握率58.1％。06シート）。とくに区域内最大の特定施設（さわやか東神楽館・定員100人）が回答していないため、入所前の居場所・退去先の集計は定員56人分の2施設に基づく（点検事項No.32）。定員・入居者数・要介護度別の内訳・従業者数は介護サービス情報公表システムの個別画面（記入日 令和7年10月6日）により補うことができるが、入所前の居場所と退去先は公表されていない。注2）入所率は調査に回答した施設の定員に対するものである。区域内の定員は北海道の名簿による（06シート）。注3）区域内・区域外の別は、調査票の「市内／市外」の選択肢による。「市内」が町単位か広域連合単位かが定義されていないため、介護サービス自給率（δ）との接続には確認を要する（点検事項No.25）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="33">
     <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="E16"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="E37"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A47:F47"/>
     <mergeCell ref="D52:E52"/>
     <mergeCell ref="E18"/>
-    <mergeCell ref="D49:E49"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="A4:F4"/>
@@ -7291,7 +7494,9 @@
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="E38"/>
     <mergeCell ref="E19"/>
-    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="D55:E55"/>
     <mergeCell ref="D30:E30"/>
@@ -7338,6 +7543,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -7446,7 +7652,7 @@
       <c r="B9" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="20" t="n">
         <v>348</v>
       </c>
       <c r="D9" s="12" t="inlineStr"/>
@@ -7457,6 +7663,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -7557,7 +7764,7 @@
       <c r="F16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>無回答・無効</t>
         </is>
@@ -7599,6 +7806,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
@@ -7663,7 +7871,7 @@
       <c r="F24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>無回答・無効</t>
         </is>
@@ -7698,6 +7906,7 @@
       <c r="E26" s="12" t="inlineStr"/>
       <c r="F26" s="12" t="inlineStr"/>
     </row>
+    <row r="27"/>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
@@ -7762,7 +7971,7 @@
       <c r="F31" s="5" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>無回答・無効</t>
         </is>
@@ -7800,10 +8009,12 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>勤続1年未満は有効回答316人の19.9％である。定着の指標として代表KPI H14と対応する。</t>
-        </is>
-      </c>
-    </row>
+          <t>勤続1年未満は有効回答316人の19.9％である。代表KPI H14は「採用率と離職率の差」であり、本値は定着の補足指標として併せて見るものである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
@@ -7921,6 +8132,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
@@ -8075,7 +8287,7 @@
       <c r="F51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>無回答・無効</t>
         </is>
@@ -8117,6 +8329,8 @@
         </is>
       </c>
     </row>
+    <row r="55"/>
+    <row r="56"/>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
@@ -8137,7 +8351,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>介護職員に対する割合</t>
+          <t>割合（分母は下欄のとおり）</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
@@ -8166,7 +8380,7 @@
       <c r="E59" s="9" t="n"/>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>分母は回答全体の介護職員348人</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8402,7 @@
       <c r="E60" s="9" t="n"/>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>分母は回答全体の介護職員348人</t>
         </is>
       </c>
     </row>
@@ -8225,17 +8439,18 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>10.6％</t>
+          <t>11.6％</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
       <c r="E62" s="9" t="n"/>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>13事業所に配置されている。介護職員に対する割合は10.6％である</t>
-        </is>
-      </c>
-    </row>
+          <t>13事業所に配置されている。いずれも施設・通所系であり訪問系3事業所には配置がない。施設・通所系の介護職員319人に対する割合は11.6％である（訪問系を含む回答全体348人を分母とすると10.6％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
     <row r="64" ht="78" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
@@ -8296,6 +8511,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -8505,7 +8721,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>代表KPI H06（在宅生活継続困難割合）の基準値。①在宅生活改善調査とは母集団が異なるため、代替ではなく補完である。</t>
+          <t>代表KPI H06（在宅生活継続困難割合）の補完指標である。H06の基準値は①在宅生活改善調査による73.5％（有効回答98票中72票）。本調査とは母集団・設問・分母がいずれも異なるため、同じH06の基準値として置き換えることはできない。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -8651,6 +8867,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="65" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
@@ -8698,6 +8915,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -8886,15 +9104,15 @@
       <c r="B11" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="20" t="n">
         <v>717</v>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>14施設・531人</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>+186人</t>
         </is>
@@ -8905,6 +9123,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -9037,15 +9256,15 @@
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="20" t="n">
         <v>339</v>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>4施設・121人</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>+218</t>
         </is>
@@ -9056,6 +9275,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -9105,7 +9325,7 @@
       <c r="C22" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -9129,7 +9349,7 @@
       <c r="C23" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -9173,7 +9393,7 @@
       <c r="C25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -9193,7 +9413,7 @@
       <c r="C26" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -9217,7 +9437,7 @@
       <c r="C27" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -9241,7 +9461,7 @@
       <c r="C28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>±0</t>
         </is>
@@ -9277,6 +9497,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -9488,6 +9709,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41" ht="78" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
@@ -9539,6 +9761,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -9580,13 +9803,13 @@
       <c r="B5" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="23" t="n">
         <v>6</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -9604,13 +9827,13 @@
       <c r="B6" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="23" t="n">
         <v>5</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -9631,7 +9854,7 @@
       <c r="C7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="14" t="n">
@@ -9652,13 +9875,13 @@
       <c r="B8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -9676,13 +9899,13 @@
       <c r="B9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -9700,13 +9923,13 @@
       <c r="B10" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="23" t="n">
         <v>8</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -9724,13 +9947,13 @@
       <c r="B11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="23" t="n">
         <v>5</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -9739,6 +9962,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -9858,6 +10082,7 @@
       <c r="E18" s="12" t="inlineStr"/>
       <c r="F18" s="12" t="inlineStr"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="65" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
@@ -9909,6 +10134,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10235,6 +10461,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -10394,6 +10621,7 @@
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr"/>
     </row>
+    <row r="24"/>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
@@ -10433,7 +10661,7 @@
           <t>区域内の小規模多機能5事業所はすべて社会福祉法人美瑛慈光会が美瑛町で運営している。小規模多機能の利用者票が同一法人に集中するのは必然である。</t>
         </is>
       </c>
-      <c r="D27" s="24" t="n"/>
+      <c r="D27" s="16" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -10453,7 +10681,7 @@
           <t>回答者である事業所が自らの提供するサービスを挙げる構造がある。</t>
         </is>
       </c>
-      <c r="D28" s="24" t="n"/>
+      <c r="D28" s="16" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -10473,7 +10701,7 @@
           <t>小規模多機能は地域密着型サービスであり、実施地域外の利用は想定されていない。東川町・東神楽町では選択肢が実質的に1つである。</t>
         </is>
       </c>
-      <c r="D29" s="24" t="n"/>
+      <c r="D29" s="16" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -10481,6 +10709,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="52" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -1793,7 +1793,7 @@
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>定着の**補足指標**。代表KPI H14は「採用率と離職率の差」であり、本値はH14そのものではない</t>
+          <t>定着の補足指標。代表KPI H14は「採用率と離職率の差」であり、本値はH14そのものではない</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       <c r="E58" s="9" t="n"/>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>4サービスのいずれかを「より適切と思われるサービス」として挙げた実人数。**複数を選んでいても1人1票として数える**（延べ件数ではない）</t>
+          <t>4サービスのいずれかを「より適切と思われるサービス」として挙げた実人数。複数を選んでいても1人1票として数える（延べ件数ではない）</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（926段落145表36図）の本文と表を章節ごとに読んで判定している。固定値では書いていない。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（928段落145表36図）の本文と表を章節ごとに読んで判定している。固定値では書いていない。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>所見と計画素案の反映先を対応させる。反映済みかどうかは計画素案の実物を読んで判定する。</t>
+          <t>所見と計画素案の反映先を対応させ、反映済みかどうかを示す。</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>所見20件。反映済みのものは計画素案から機械的に判定する。</t>
+          <t>所見20件。反映済み・着手可・決定待ちに区分する。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -3665,10 +3665,10 @@
       </c>
     </row>
     <row r="31"/>
-    <row r="32" ht="52" customHeight="1">
+    <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（928段落145表36図）の本文と表を章節ごとに読んで判定している。固定値では書いていない。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（928段落145表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（928段落145表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（943段落147表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（943段落147表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（916段落141表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（916段落141表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（927段落143表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（927段落143表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（928段落143表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（928段落143表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（942段落145表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（942段落145表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（949段落146表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（949段落146表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（951段落146表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（951段落146表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（973段落148表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（973段落148表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1000段落151表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1000段落151表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1001段落151表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1001段落151表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1024段落152表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1024段落152表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1027段落153表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1027段落153表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1030段落153表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1030段落153表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1038段落153表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1038段落153表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1060段落156表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1060段落156表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1059段落156表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -3668,7 +3668,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1059段落156表36図）に反映されているものである。</t>
+          <t>注1）所見20件のうち11件は反映済みであり、点検事項の取扱いの決定を要せず着手できるものは0件である。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。注4）「反映済」は、計画素案（1062段落156表36図）に反映されているものである。</t>
         </is>
       </c>
     </row>
